--- a/Collections/Russia/#Russia#USSR#Regular#[1921-1991]#circulation_quality.xlsx
+++ b/Collections/Russia/#Russia#USSR#Regular#[1921-1991]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Russia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A334AA3-D468-4612-AFAF-DB2BBBA9D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34364574-CA85-4CCC-A177-4E085A414F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="полкопейки" sheetId="12" r:id="rId1"/>
@@ -51,6 +51,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1242,6 +1245,15 @@
   </cellStyles>
   <dxfs count="121">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9BE5FF"/>
@@ -1280,15 +1292,6 @@
           <bgColor rgb="FF9BE5FF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -2221,9 +2224,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="6" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4344,7 +4347,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F11))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13 F11 F15 F17 F19 F21 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53 F55 F57 F59 F61 F63 F65 F67 F69 F71 F73">
+  <conditionalFormatting sqref="F11 F13 F15 F17 F19 F21 F23 F25 F27 F29 F31 F33 F35 F37 F39 F41 F43 F45 F47 F49 F51 F53 F55 F57 F59 F61 F63 F65 F67 F69 F71 F73">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4361,7 +4364,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F12))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14 F12 F16 F18 F20 F22 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54 F56 F58 F60 F62 F64 F66 F68 F70 F72">
+  <conditionalFormatting sqref="F12 F14 F16 F18 F20 F22 F24 F26 F28 F30 F32 F34 F36 F38 F40 F42 F44 F46 F48 F50 F52 F54 F56 F58 F60 F62 F64 F66 F68 F70 F72">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6696,7 +6699,7 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I43 I77:I78">
-    <cfRule type="containsText" dxfId="25" priority="41" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="41" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="42">
@@ -6711,7 +6714,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I5">
-    <cfRule type="containsText" dxfId="24" priority="39" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="19" priority="39" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="40">
@@ -6726,7 +6729,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="23" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="18" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -6741,7 +6744,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="22" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -6756,7 +6759,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I76">
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="16" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I76))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -6771,7 +6774,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I79">
-    <cfRule type="containsText" dxfId="20" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="15" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I79))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -6786,7 +6789,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47:I50 I44">
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="14" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I44))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="18">
@@ -6801,7 +6804,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I45">
-    <cfRule type="containsText" dxfId="18" priority="15" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I45))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
@@ -6816,7 +6819,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I46">
-    <cfRule type="containsText" dxfId="17" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I46))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
@@ -6831,7 +6834,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51:I55">
-    <cfRule type="containsText" dxfId="16" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I51))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6848,7 +6851,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56:I60">
-    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I56))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6865,7 +6868,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61:I65">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I61))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6882,7 +6885,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I66:I70">
-    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I66))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6899,7 +6902,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I71:I75">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I71))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8705,7 +8708,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F72 F74">
-    <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="20">
@@ -8720,7 +8723,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F73))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -10500,7 +10503,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F72">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -10515,7 +10518,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F73))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -20995,7 +20998,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H26 H24">
+  <conditionalFormatting sqref="H24 H26">
     <cfRule type="containsText" dxfId="60" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H24))))</formula>
     </cfRule>
@@ -22015,7 +22018,7 @@
         <v>5</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="11" t="str">
         <f t="shared" si="1"/>
@@ -24958,7 +24961,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G40">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="38" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G40))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
@@ -24973,7 +24976,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="37" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G41))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -24988,7 +24991,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G42">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="36" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G42))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -25003,7 +25006,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G45">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G45))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -25018,7 +25021,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G46">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(G46))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -27248,7 +27251,7 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="I3:I5 I9:I11 I7 I45 I48:I51 I77:I79">
-    <cfRule type="containsText" dxfId="37" priority="33" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="33" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
@@ -27263,7 +27266,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="36" priority="31" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
@@ -27278,7 +27281,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I12:I44">
-    <cfRule type="containsText" dxfId="35" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="27" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
@@ -27293,7 +27296,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="34" priority="25" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="25" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I6))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
@@ -27308,7 +27311,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I46">
-    <cfRule type="containsText" dxfId="33" priority="23" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="23" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I46))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="24">
@@ -27323,7 +27326,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="containsText" dxfId="32" priority="21" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="21" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I47))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="22">
@@ -27338,7 +27341,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I80">
-    <cfRule type="containsText" dxfId="31" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I80))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
@@ -27353,7 +27356,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I52:I56">
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I52))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27370,7 +27373,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57:I61">
-    <cfRule type="containsText" dxfId="29" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I57))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27387,7 +27390,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I62:I66">
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I62))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27404,7 +27407,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I67:I71">
-    <cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I67))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27421,7 +27424,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I72:I76">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I72))))</formula>
     </cfRule>
   </conditionalFormatting>
